--- a/Lora_and_SigFox_Devices/MeteoWind_IoT_Pro_Gen2_Gen3/Customer_uplinks_downlinks_wind.xlsx
+++ b/Lora_and_SigFox_Devices/MeteoWind_IoT_Pro_Gen2_Gen3/Customer_uplinks_downlinks_wind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Desktop\uplinks downlinks Gen2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F3B8DC-6FC3-415F-936F-553EA2E828FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6B161F-456E-44CB-B8B5-1FF5429914DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
   <si>
     <t>UPLINKS</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>O1O2 - counter from 5 to 4095, when can be timesync, default = 1000</t>
+  </si>
+  <si>
+    <t>after downlink sent, wait for downlink to be processed and then register device with new appkey and appeui</t>
   </si>
 </sst>
 </file>
@@ -237,7 +240,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -266,6 +269,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF008000"/>
       </patternFill>
     </fill>
   </fills>
@@ -302,7 +311,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -319,6 +327,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,60 +610,60 @@
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="15"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -666,8 +675,8 @@
       <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
@@ -726,28 +735,28 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>100</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="14" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -755,13 +764,16 @@
       </c>
       <c r="D16" s="2" t="s">
         <v>21</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>103</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -775,7 +787,7 @@
       <c r="A18" s="1">
         <v>104</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="20" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -789,7 +801,7 @@
       <c r="A19" s="1">
         <v>107</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -803,7 +815,7 @@
       <c r="A20" s="1">
         <v>108</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="20" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -820,7 +832,7 @@
       <c r="A21" s="1">
         <v>109</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="20" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -834,7 +846,7 @@
       <c r="A22" s="1">
         <v>110</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="20" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -848,7 +860,7 @@
       <c r="A23" s="1">
         <v>111</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -862,39 +874,39 @@
       <c r="A24" s="1">
         <v>112</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>120</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="20" t="s">
         <v>35</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -911,32 +923,32 @@
       <c r="A28" s="1">
         <v>121</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F28" s="11"/>
+      <c r="F28" s="10"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -953,7 +965,7 @@
       <c r="A32" s="1">
         <v>132</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="20" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -964,12 +976,12 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Lora_and_SigFox_Devices/MeteoWind_IoT_Pro_Gen2_Gen3/Customer_uplinks_downlinks_wind.xlsx
+++ b/Lora_and_SigFox_Devices/MeteoWind_IoT_Pro_Gen2_Gen3/Customer_uplinks_downlinks_wind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Documents\GitHub\P_SRC_device_decoders\Lora_and_SigFox_Devices\MeteoWind_IoT_Pro_Gen2_Gen3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6B161F-456E-44CB-B8B5-1FF5429914DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E3A055-1369-454A-A10A-DCB34C4AA9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
   <si>
     <t>UPLINKS</t>
   </si>
@@ -99,12 +99,6 @@
     <t>config OTAA</t>
   </si>
   <si>
-    <t>24b</t>
-  </si>
-  <si>
-    <t>24b - AppKey + AppEUI</t>
-  </si>
-  <si>
     <t>config ADR - Automatic Data Rate</t>
   </si>
   <si>
@@ -202,6 +196,9 @@
   </si>
   <si>
     <t>after downlink sent, wait for downlink to be processed and then register device with new appkey and appeui</t>
+  </si>
+  <si>
+    <t>24B / 16B APPKEY + 8B APPEUI /</t>
   </si>
 </sst>
 </file>
@@ -325,9 +322,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -594,7 +591,7 @@
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32" style="2" customWidth="1"/>
     <col min="4" max="7" width="26.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -714,7 +711,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>16</v>
@@ -735,22 +732,22 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -760,13 +757,10 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -774,86 +768,86 @@
         <v>103</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>104</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>25</v>
+      <c r="B18" s="18" t="s">
+        <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>107</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>27</v>
+      <c r="B19" s="18" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>108</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>109</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>33</v>
+      <c r="B21" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>110</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>34</v>
+      <c r="B22" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,13 +855,13 @@
         <v>111</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -875,65 +869,65 @@
         <v>112</v>
       </c>
       <c r="B24" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="A26" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>120</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>121</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="F28" s="10"/>
     </row>
@@ -941,47 +935,47 @@
       <c r="A29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="A30" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>130</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>132</v>
       </c>
-      <c r="B32" s="20" t="s">
-        <v>42</v>
+      <c r="B32" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="6">
